--- a/content/day06/test_data/test_cases.xlsx
+++ b/content/day06/test_data/test_cases.xlsx
@@ -39,7 +39,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -54,20 +54,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF00FF00"/>
-        <bgColor rgb="FF00FF00"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00ff0000"/>
         <bgColor rgb="00ff0000"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="0000FF00"/>
-        <bgColor rgb="0000FF00"/>
+        <fgColor rgb="00FFD700"/>
+        <bgColor rgb="00FFD700"/>
       </patternFill>
     </fill>
   </fills>
@@ -90,7 +84,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -102,7 +96,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -476,7 +469,8 @@
     <col width="12" bestFit="1" customWidth="1" min="3" max="3"/>
     <col width="24.6640625" bestFit="1" customWidth="1" min="4" max="4"/>
     <col width="20.44140625" bestFit="1" customWidth="1" min="5" max="5"/>
-    <col width="10.44140625" bestFit="1" customWidth="1" min="6" max="7"/>
+    <col width="10.44140625" bestFit="1" customWidth="1" min="6" max="6"/>
+    <col width="68.77734375" bestFit="1" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="18.75" customHeight="1">
@@ -537,93 +531,26 @@
           <t>Selenium</t>
         </is>
       </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="20.25" customHeight="1">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>TC002</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>搜索Python</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Python</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Python</t>
-        </is>
-      </c>
-      <c r="F3" s="7" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="20.25" customHeight="1">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>TC003</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>搜索错误</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">xxxxxxxxxx	</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>找不到</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="20.25" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>TC004</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>搜索美女</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>美女</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>美女</t>
-        </is>
-      </c>
-      <c r="F5" s="7" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-    </row>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>百度一下，你就知道</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>Error</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">程序出错啦，原因是：Message: 超时也没能找到该元素百度一下
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20.25" customHeight="1"/>
+    <row r="4" ht="20.25" customHeight="1"/>
+    <row r="5" ht="20.25" customHeight="1"/>
     <row r="6" ht="20.25" customHeight="1">
       <c r="A6" s="3" t="n"/>
       <c r="B6" s="3" t="n"/>
@@ -660,75 +587,90 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="13.5546875" bestFit="1" customWidth="1" style="2" min="1" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.4" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="20.25" customHeight="1">
+      <c r="A1" t="inlineStr">
         <is>
           <t>TC002</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>搜索Selenium</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Selenium</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Selenium</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="14.4" customHeight="1">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>搜索Python</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20.25" customHeight="1">
+      <c r="A2" t="inlineStr">
         <is>
           <t>TC003</t>
         </is>
       </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t>搜索Python</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="inlineStr">
-        <is>
-          <t>Python</t>
-        </is>
-      </c>
-      <c r="D2" s="1" t="inlineStr">
-        <is>
-          <t>Python</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="14.4" customHeight="1">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>搜索错误</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">xxxxxxxxxx	</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>找不到</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20.25" customHeight="1">
+      <c r="A3" t="inlineStr">
         <is>
           <t>TC004</t>
         </is>
       </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>搜索错误</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">xxxxxxxxxx	</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>找不到</t>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>搜索美女</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>美女</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>美女</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>

--- a/content/day06/test_data/test_cases.xlsx
+++ b/content/day06/test_data/test_cases.xlsx
@@ -17,19 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <name val="宋体"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <family val="2"/>
-      <color rgb="FF000000"/>
-      <sz val="11"/>
     </font>
     <font>
       <name val="宋体"/>
@@ -48,20 +42,20 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
-        <bgColor rgb="FFFF0000"/>
+        <fgColor rgb="FF00FF00"/>
+        <bgColor rgb="FF00FF00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0000FF00"/>
+        <bgColor rgb="0000FF00"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00ff0000"/>
         <bgColor rgb="00ff0000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFD700"/>
-        <bgColor rgb="00FFD700"/>
       </patternFill>
     </fill>
   </fills>
@@ -84,11 +78,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
@@ -533,7 +524,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>百度一下，你就知道</t>
+          <t>Selenium_百度搜索</t>
         </is>
       </c>
       <c r="F2" s="5" t="inlineStr">
@@ -543,37 +534,165 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t xml:space="preserve">程序出错啦，原因是：Message: 超时也没能找到该元素百度一下
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="20.25" customHeight="1"/>
-    <row r="4" ht="20.25" customHeight="1"/>
-    <row r="5" ht="20.25" customHeight="1"/>
+          <t>程序出错啦，原因是：'bool' object has no attribute 'input_text'</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20.25" customHeight="1">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>TC002</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>搜索Python</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Python_百度搜索</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>Error</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>程序出错啦，原因是：'bool' object has no attribute 'input_text'</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="20.25" customHeight="1">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>TC003</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>搜索错误</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">xxxxxxxxxx	</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>找不到</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>Error</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>程序出错啦，原因是：'bool' object has no attribute 'input_text'</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="20.25" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>TC004</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>搜索美女</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>美女</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>美女</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>美女_百度搜索</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>Error</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>程序出错啦，原因是：'bool' object has no attribute 'input_text'</t>
+        </is>
+      </c>
+    </row>
     <row r="6" ht="20.25" customHeight="1">
-      <c r="A6" s="3" t="n"/>
-      <c r="B6" s="3" t="n"/>
-      <c r="C6" s="3" t="n"/>
-      <c r="D6" s="3" t="n"/>
-    </row>
-    <row r="7" ht="20.25" customHeight="1">
-      <c r="A7" s="3" t="n"/>
-      <c r="B7" s="3" t="n"/>
-      <c r="C7" s="3" t="n"/>
-      <c r="D7" s="3" t="n"/>
-    </row>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>TC005</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>搜索美女</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>美女</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>美女</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>美女_百度搜索</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>Error</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>程序出错啦，原因是：'bool' object has no attribute 'input_text'</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="20.25" customHeight="1"/>
     <row r="8" ht="20.25" customHeight="1">
-      <c r="A8" s="3" t="n"/>
-      <c r="B8" s="3" t="n"/>
-      <c r="C8" s="3" t="n"/>
-      <c r="D8" s="3" t="n"/>
+      <c r="A8" s="2" t="n"/>
+      <c r="B8" s="2" t="n"/>
+      <c r="C8" s="2" t="n"/>
+      <c r="D8" s="2" t="n"/>
     </row>
     <row r="9" ht="20.25" customHeight="1">
-      <c r="A9" s="3" t="n"/>
-      <c r="B9" s="3" t="n"/>
-      <c r="C9" s="3" t="n"/>
-      <c r="D9" s="3" t="n"/>
+      <c r="A9" s="2" t="n"/>
+      <c r="B9" s="2" t="n"/>
+      <c r="C9" s="2" t="n"/>
+      <c r="D9" s="2" t="n"/>
     </row>
     <row r="10"/>
   </sheetData>
@@ -590,7 +709,7 @@
   <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col width="13.5546875" bestFit="1" customWidth="1" style="2" min="1" max="4"/>
+    <col width="13.5546875" bestFit="1" customWidth="1" style="1" min="1" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="20.25" customHeight="1">
@@ -675,22 +794,22 @@
       </c>
     </row>
     <row r="4" ht="14.4" customHeight="1">
-      <c r="A4" s="1" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>TC005</t>
         </is>
       </c>
-      <c r="B4" s="1" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>搜索美女</t>
         </is>
       </c>
-      <c r="C4" s="1" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>美女</t>
         </is>
       </c>
-      <c r="D4" s="1" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>美女</t>
         </is>
@@ -698,5 +817,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" horizontalDpi="1200" verticalDpi="1200"/>
 </worksheet>
 </file>
--- a/content/day06/test_data/test_cases.xlsx
+++ b/content/day06/test_data/test_cases.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="12" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -527,14 +527,14 @@
           <t>Selenium_百度搜索</t>
         </is>
       </c>
-      <c r="F2" s="5" t="inlineStr">
-        <is>
-          <t>Error</t>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>程序出错啦，原因是：'bool' object has no attribute 'input_text'</t>
+          <t>Selenium_百度搜索在期望值:Selenium 里面</t>
         </is>
       </c>
     </row>
@@ -564,14 +564,14 @@
           <t>Python_百度搜索</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr">
-        <is>
-          <t>Error</t>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>程序出错啦，原因是：'bool' object has no attribute 'input_text'</t>
+          <t>Python_百度搜索在期望值:Python 里面</t>
         </is>
       </c>
     </row>
@@ -603,7 +603,8 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>程序出错啦，原因是：'bool' object has no attribute 'input_text'</t>
+          <t xml:space="preserve">程序出错啦，原因是：Message: 
+</t>
         </is>
       </c>
     </row>
@@ -633,14 +634,14 @@
           <t>美女_百度搜索</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
-        <is>
-          <t>Error</t>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>程序出错啦，原因是：'bool' object has no attribute 'input_text'</t>
+          <t>美女_百度搜索在期望值:美女 里面</t>
         </is>
       </c>
     </row>
@@ -670,14 +671,14 @@
           <t>美女_百度搜索</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
-        <is>
-          <t>Error</t>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>程序出错啦，原因是：'bool' object has no attribute 'input_text'</t>
+          <t>美女_百度搜索在期望值:美女 里面</t>
         </is>
       </c>
     </row>
@@ -694,7 +695,6 @@
       <c r="C9" s="2" t="n"/>
       <c r="D9" s="2" t="n"/>
     </row>
-    <row r="10"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/content/day06/test_data/test_cases.xlsx
+++ b/content/day06/test_data/test_cases.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\16531\Desktop\selenium-learning\content\day06\test_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{279A56E8-8A55-499C-B3C1-C31A116890AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28EF605E-E44F-4C0F-B482-FE03E8091D7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="24">
   <si>
     <t>case_id</t>
   </si>
@@ -56,12 +56,6 @@
     <t>Selenium_百度搜索</t>
   </si>
   <si>
-    <t>Pass</t>
-  </si>
-  <si>
-    <t>Selenium_百度搜索在期望值:Selenium 里面</t>
-  </si>
-  <si>
     <t>TC002</t>
   </si>
   <si>
@@ -74,9 +68,6 @@
     <t>Python_百度搜索</t>
   </si>
   <si>
-    <t>Python_百度搜索在期望值:Python 里面</t>
-  </si>
-  <si>
     <t>TC003</t>
   </si>
   <si>
@@ -89,13 +80,6 @@
     <t>找不到</t>
   </si>
   <si>
-    <t>Error</t>
-  </si>
-  <si>
-    <t xml:space="preserve">程序出错啦，原因是：Message: 
-</t>
-  </si>
-  <si>
     <t>TC004</t>
   </si>
   <si>
@@ -106,9 +90,6 @@
   </si>
   <si>
     <t>美女_百度搜索</t>
-  </si>
-  <si>
-    <t>美女_百度搜索在期望值:美女 里面</t>
   </si>
   <si>
     <t>TC005</t>
@@ -134,24 +115,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF00FF00"/>
-        <bgColor rgb="FF00FF00"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
-        <bgColor rgb="FFFF0000"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -173,14 +142,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -537,102 +504,27 @@
       <c r="E2" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G2" t="s">
-        <v>12</v>
-      </c>
     </row>
     <row r="3" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" t="s">
         <v>13</v>
       </c>
-      <c r="B3" t="s">
+      <c r="D3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" t="s">
         <v>14</v>
       </c>
-      <c r="C3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D3" t="s">
-        <v>15</v>
-      </c>
-      <c r="E3" t="s">
-        <v>16</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D4" t="s">
-        <v>21</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>24</v>
-      </c>
-      <c r="B5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C5" t="s">
-        <v>26</v>
-      </c>
-      <c r="D5" t="s">
-        <v>26</v>
-      </c>
-      <c r="E5" t="s">
-        <v>27</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G5" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>29</v>
-      </c>
-      <c r="B6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C6" t="s">
-        <v>26</v>
-      </c>
-      <c r="D6" t="s">
-        <v>26</v>
-      </c>
-      <c r="E6" t="s">
-        <v>27</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G6" t="s">
-        <v>28</v>
-      </c>
-    </row>
+    </row>
+    <row r="4" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="7" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="8" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2"/>
@@ -707,67 +599,67 @@
     </row>
     <row r="3" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" t="s">
         <v>13</v>
       </c>
-      <c r="B3" t="s">
+      <c r="D3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" t="s">
         <v>14</v>
-      </c>
-      <c r="C3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D3" t="s">
-        <v>15</v>
-      </c>
-      <c r="E3" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" t="s">
         <v>18</v>
-      </c>
-      <c r="B4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D4" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="B5" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="C5" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="D5" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="E5" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="B6" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="C6" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="D6" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="E6" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
